--- a/fix-errors/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-pregnancy-history</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-pregnancy-history|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,115 +115,115 @@
     <t>equivalent</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse</t>
+    <t>Organizer</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.header.identifier</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.id</t>
+    <t>Organizer.id</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.header.status</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.statusCode</t>
+    <t>Organizer.statusCode</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.directSubject[x]</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.subject</t>
+    <t>Organizer.subject</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.type</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.code</t>
+    <t>Organizer.code</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.observationDate[x]</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.effectiveTime</t>
+    <t>Organizer.effectiveTime</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.result</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.component:frObservationSurLaGrossesse</t>
+    <t>Organizer.component:frObservationSurLaGrossesse</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.component</t>
   </si>
   <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.component:frNaissance</t>
+    <t>Organizer.component:frNaissance</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-history-document|0.1.0</t>
   </si>
   <si>
-    <t>FRObservationPregnancyHistoryDocument</t>
-  </si>
-  <si>
-    <t>FRObservationPregnancyHistoryDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRObservationPregnancyHistoryDocument.status</t>
-  </si>
-  <si>
-    <t>FRObservationPregnancyHistoryDocument.focus</t>
-  </si>
-  <si>
-    <t>FRObservationPregnancyHistoryDocument.code</t>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Observation.identifier</t>
+  </si>
+  <si>
+    <t>Observation.status</t>
+  </si>
+  <si>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t>Observation.code</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.method</t>
   </si>
   <si>
-    <t>FRObservationPregnancyHistoryDocument.method</t>
-  </si>
-  <si>
-    <t>FRObservationPregnancyHistoryDocument.effective[x]</t>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.result.value[x]</t>
   </si>
   <si>
-    <t>FRObservationPregnancyHistoryDocument.value[x]</t>
+    <t>Observation.value[x]</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.result.dataAbsentReason</t>
   </si>
   <si>
-    <t>FRObservationPregnancyHistoryDocument.dataAbsentReason</t>
+    <t>Observation.dataAbsentReason</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.interpretation</t>
   </si>
   <si>
-    <t>FRObservationPregnancyHistoryDocument.interpretation</t>
+    <t>Observation.interpretation</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.note</t>
   </si>
   <si>
-    <t>FRObservationPregnancyHistoryDocument.note</t>
-  </si>
-  <si>
-    <t>FRObservationPregnancyHistoryDocument.component</t>
+    <t>Observation.note</t>
+  </si>
+  <si>
+    <t>Observation.component</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.derivedFrom[x]</t>
   </si>
   <si>
-    <t>FRObservationPregnancyHistoryDocument.derivedFrom</t>
+    <t>Observation.derivedFrom</t>
   </si>
   <si>
     <t>FRLMPregnancyHistory.hasMember[x]</t>
   </si>
   <si>
-    <t>FRObservationPregnancyHistoryDocument.hasMember</t>
+    <t>Observation.hasMember</t>
   </si>
 </sst>
 </file>
